--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/49.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/49.xlsx
@@ -426,13 +426,13 @@
         <v>-8.386243890559257</v>
       </c>
       <c r="E2">
-        <v>-17.84216702455877</v>
+        <v>-19.32445430759348</v>
       </c>
       <c r="F2">
-        <v>1.873562311136483</v>
+        <v>1.945704828246291</v>
       </c>
       <c r="G2">
-        <v>-14.42106772443401</v>
+        <v>-13.7787521980649</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.751078491103336</v>
       </c>
       <c r="E3">
-        <v>-17.35511153113779</v>
+        <v>-18.70920224348936</v>
       </c>
       <c r="F3">
-        <v>2.019093209929911</v>
+        <v>1.902092941223703</v>
       </c>
       <c r="G3">
-        <v>-14.51660541196958</v>
+        <v>-14.11803378853305</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.99668576550164</v>
       </c>
       <c r="E4">
-        <v>-17.96265613248086</v>
+        <v>-18.17664464323931</v>
       </c>
       <c r="F4">
-        <v>2.082166760713871</v>
+        <v>2.566523121539575</v>
       </c>
       <c r="G4">
-        <v>-14.54653343381327</v>
+        <v>-12.89741772780883</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.183508970158191</v>
       </c>
       <c r="E5">
-        <v>-19.06426630500877</v>
+        <v>-19.58457891154208</v>
       </c>
       <c r="F5">
-        <v>2.136383407227099</v>
+        <v>2.096994537223982</v>
       </c>
       <c r="G5">
-        <v>-13.71645656614807</v>
+        <v>-13.73802239484752</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.323172843102365</v>
       </c>
       <c r="E6">
-        <v>-19.49376036531825</v>
+        <v>-20.29002459245697</v>
       </c>
       <c r="F6">
-        <v>2.019815546305152</v>
+        <v>2.499006208006999</v>
       </c>
       <c r="G6">
-        <v>-13.86319935672955</v>
+        <v>-13.43669305354669</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.445792736856387</v>
       </c>
       <c r="E7">
-        <v>-19.72875646699829</v>
+        <v>-20.42538520902024</v>
       </c>
       <c r="F7">
-        <v>1.973632406864274</v>
+        <v>2.37920937094894</v>
       </c>
       <c r="G7">
-        <v>-13.73820778386563</v>
+        <v>-12.35366681586389</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.57397529662899</v>
       </c>
       <c r="E8">
-        <v>-21.02269545910597</v>
+        <v>-20.68800953062108</v>
       </c>
       <c r="F8">
-        <v>2.371253730412453</v>
+        <v>2.445221969278033</v>
       </c>
       <c r="G8">
-        <v>-12.20418092405871</v>
+        <v>-12.57555614259978</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.73491044308076</v>
       </c>
       <c r="E9">
-        <v>-21.4832729650041</v>
+        <v>-24.28924678590288</v>
       </c>
       <c r="F9">
-        <v>1.816908607724219</v>
+        <v>2.731522311033598</v>
       </c>
       <c r="G9">
-        <v>-12.30780190090598</v>
+        <v>-11.78570048881025</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.94644397606219</v>
       </c>
       <c r="E10">
-        <v>-21.73994687175886</v>
+        <v>-23.19175752472194</v>
       </c>
       <c r="F10">
-        <v>1.822710493013426</v>
+        <v>2.94645714430318</v>
       </c>
       <c r="G10">
-        <v>-10.91409976231027</v>
+        <v>-11.47053915802559</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.225598879012127</v>
       </c>
       <c r="E11">
-        <v>-21.79744037776024</v>
+        <v>-22.76595869920272</v>
       </c>
       <c r="F11">
-        <v>1.715589333953006</v>
+        <v>3.061749319424815</v>
       </c>
       <c r="G11">
-        <v>-11.24260910239876</v>
+        <v>-13.85429412141722</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5854952904307402</v>
       </c>
       <c r="E12">
-        <v>-23.67381811131246</v>
+        <v>-26.180917176179</v>
       </c>
       <c r="F12">
-        <v>1.37618401473877</v>
+        <v>2.887750746466779</v>
       </c>
       <c r="G12">
-        <v>-9.582839269990803</v>
+        <v>-11.02366631262325</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.03587742809938472</v>
       </c>
       <c r="E13">
-        <v>-25.26712546311921</v>
+        <v>-25.85233563065644</v>
       </c>
       <c r="F13">
-        <v>2.532468937610488</v>
+        <v>2.728497113278574</v>
       </c>
       <c r="G13">
-        <v>-10.09948401063317</v>
+        <v>-9.3368001525774</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.4081964207209132</v>
       </c>
       <c r="E14">
-        <v>-26.12671587078119</v>
+        <v>-26.1241210551748</v>
       </c>
       <c r="F14">
-        <v>2.316763722656302</v>
+        <v>3.08814773181723</v>
       </c>
       <c r="G14">
-        <v>-9.725939904641306</v>
+        <v>-9.084644838177192</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.7401446011902134</v>
       </c>
       <c r="E15">
-        <v>-25.18841152791789</v>
+        <v>-28.71920837001037</v>
       </c>
       <c r="F15">
-        <v>2.333417220922183</v>
+        <v>3.241531553589197</v>
       </c>
       <c r="G15">
-        <v>-9.419434436330455</v>
+        <v>-8.414491428097763</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.9579199687028455</v>
       </c>
       <c r="E16">
-        <v>-26.80174379178656</v>
+        <v>-26.79383707616917</v>
       </c>
       <c r="F16">
-        <v>2.197974180360047</v>
+        <v>2.679832185098908</v>
       </c>
       <c r="G16">
-        <v>-7.830391334636331</v>
+        <v>-7.481223423609581</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.062843856619407</v>
       </c>
       <c r="E17">
-        <v>-26.65849004502791</v>
+        <v>-29.16849639020738</v>
       </c>
       <c r="F17">
-        <v>2.288304332165722</v>
+        <v>3.338125819694842</v>
       </c>
       <c r="G17">
-        <v>-8.126465799609706</v>
+        <v>-9.1875341026167</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.060526232638357</v>
       </c>
       <c r="E18">
-        <v>-28.13902480862165</v>
+        <v>-29.35932628489061</v>
       </c>
       <c r="F18">
-        <v>3.022908828642352</v>
+        <v>3.712615811887248</v>
       </c>
       <c r="G18">
-        <v>-7.874694388131954</v>
+        <v>-8.09093017012092</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.9580918394311172</v>
       </c>
       <c r="E19">
-        <v>-27.6291956194161</v>
+        <v>-30.25503580123777</v>
       </c>
       <c r="F19">
-        <v>2.827564884448978</v>
+        <v>2.928529616971793</v>
       </c>
       <c r="G19">
-        <v>-7.328131469310569</v>
+        <v>-7.91484013391176</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7649376716133878</v>
       </c>
       <c r="E20">
-        <v>-28.721939039837</v>
+        <v>-27.61111795117748</v>
       </c>
       <c r="F20">
-        <v>2.691586718544634</v>
+        <v>3.343483700056149</v>
       </c>
       <c r="G20">
-        <v>-6.243549932608594</v>
+        <v>-6.659881167735618</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.4958782352131699</v>
       </c>
       <c r="E21">
-        <v>-28.76324325126096</v>
+        <v>-31.82809860999323</v>
       </c>
       <c r="F21">
-        <v>2.724444739944079</v>
+        <v>4.304058540342456</v>
       </c>
       <c r="G21">
-        <v>-7.586192982517777</v>
+        <v>-6.743614660711088</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.1633360935874614</v>
       </c>
       <c r="E22">
-        <v>-30.38220214408416</v>
+        <v>-32.83199789885764</v>
       </c>
       <c r="F22">
-        <v>2.759807744369589</v>
+        <v>3.187440818921195</v>
       </c>
       <c r="G22">
-        <v>-5.499254040171952</v>
+        <v>-5.693512200155757</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.2193172324449893</v>
       </c>
       <c r="E23">
-        <v>-30.66374869432605</v>
+        <v>-30.89398084135001</v>
       </c>
       <c r="F23">
-        <v>2.528071963436428</v>
+        <v>4.088562073973776</v>
       </c>
       <c r="G23">
-        <v>-5.277171121364055</v>
+        <v>-6.977447633923355</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6395709809550515</v>
       </c>
       <c r="E24">
-        <v>-31.26627348223161</v>
+        <v>-31.39589199375316</v>
       </c>
       <c r="F24">
-        <v>2.765649391294132</v>
+        <v>3.600330610437775</v>
       </c>
       <c r="G24">
-        <v>-6.006232302100195</v>
+        <v>-5.55244592287211</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.085626120946087</v>
       </c>
       <c r="E25">
-        <v>-31.23868149010287</v>
+        <v>-32.15479178185458</v>
       </c>
       <c r="F25">
-        <v>2.859302953119838</v>
+        <v>3.840217526614484</v>
       </c>
       <c r="G25">
-        <v>-4.790044249870452</v>
+        <v>-5.732657173359933</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.545473567555858</v>
       </c>
       <c r="E26">
-        <v>-32.48384202443693</v>
+        <v>-32.57522889414872</v>
       </c>
       <c r="F26">
-        <v>2.611775176019707</v>
+        <v>3.901089276841803</v>
       </c>
       <c r="G26">
-        <v>-4.287272513981416</v>
+        <v>-4.917296584388837</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.007726573771611</v>
       </c>
       <c r="E27">
-        <v>-31.858663545308</v>
+        <v>-32.00062667697446</v>
       </c>
       <c r="F27">
-        <v>2.885810710009422</v>
+        <v>4.264038454378406</v>
       </c>
       <c r="G27">
-        <v>-4.759453421271749</v>
+        <v>-5.569291714358299</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.465472389941754</v>
       </c>
       <c r="E28">
-        <v>-31.49875628083739</v>
+        <v>-34.29853967776768</v>
       </c>
       <c r="F28">
-        <v>2.71804477339005</v>
+        <v>3.664905162955608</v>
       </c>
       <c r="G28">
-        <v>-3.670688327081482</v>
+        <v>-4.96514335716866</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.91161810371635</v>
       </c>
       <c r="E29">
-        <v>-31.28858300943039</v>
+        <v>-33.13833784429152</v>
       </c>
       <c r="F29">
-        <v>2.872488905437601</v>
+        <v>3.958519988877892</v>
       </c>
       <c r="G29">
-        <v>-3.362913026027127</v>
+        <v>-4.396953907048975</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.339106243807308</v>
       </c>
       <c r="E30">
-        <v>-29.99759431813871</v>
+        <v>-33.25036776276728</v>
       </c>
       <c r="F30">
-        <v>2.910742912098882</v>
+        <v>3.876495048652686</v>
       </c>
       <c r="G30">
-        <v>-4.523300624416954</v>
+        <v>-4.31378150296017</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.74040911316276</v>
       </c>
       <c r="E31">
-        <v>-31.93865677441649</v>
+        <v>-33.10242704541069</v>
       </c>
       <c r="F31">
-        <v>3.263491573437412</v>
+        <v>3.158224300624457</v>
       </c>
       <c r="G31">
-        <v>-3.232372907506178</v>
+        <v>-5.2107263847853</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.106378119065376</v>
       </c>
       <c r="E32">
-        <v>-31.49394930567825</v>
+        <v>-33.33099044976284</v>
       </c>
       <c r="F32">
-        <v>2.592114704081663</v>
+        <v>3.200676473283126</v>
       </c>
       <c r="G32">
-        <v>-3.712743743808885</v>
+        <v>-4.15459303900371</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.43060306442031</v>
       </c>
       <c r="E33">
-        <v>-31.22413829582724</v>
+        <v>-32.76288432855257</v>
       </c>
       <c r="F33">
-        <v>3.276579778401644</v>
+        <v>3.98481568371236</v>
       </c>
       <c r="G33">
-        <v>-4.229664107062246</v>
+        <v>-5.141876512803471</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.707629681004783</v>
       </c>
       <c r="E34">
-        <v>-31.37749506809699</v>
+        <v>-31.28494890903924</v>
       </c>
       <c r="F34">
-        <v>2.574826676385237</v>
+        <v>3.529400823205665</v>
       </c>
       <c r="G34">
-        <v>-3.721317575743714</v>
+        <v>-5.770588094587113</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.931928661949735</v>
       </c>
       <c r="E35">
-        <v>-30.34135983700898</v>
+        <v>-31.50037068182112</v>
       </c>
       <c r="F35">
-        <v>3.12370291748019</v>
+        <v>3.932520849573627</v>
       </c>
       <c r="G35">
-        <v>-4.76724632247543</v>
+        <v>-6.918021430260253</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.099415356941453</v>
       </c>
       <c r="E36">
-        <v>-29.75681761938788</v>
+        <v>-30.05270131833805</v>
       </c>
       <c r="F36">
-        <v>2.604016686925087</v>
+        <v>3.587419676097742</v>
       </c>
       <c r="G36">
-        <v>-4.402351516514262</v>
+        <v>-4.757271408934718</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.207447782491483</v>
       </c>
       <c r="E37">
-        <v>-29.93984495335589</v>
+        <v>-32.16441705335789</v>
       </c>
       <c r="F37">
-        <v>2.9241525236154</v>
+        <v>4.659839026375233</v>
       </c>
       <c r="G37">
-        <v>-4.132044484447206</v>
+        <v>-5.300920603011316</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.253291711524422</v>
       </c>
       <c r="E38">
-        <v>-28.39467075177667</v>
+        <v>-29.92347904829217</v>
       </c>
       <c r="F38">
-        <v>3.10636021753518</v>
+        <v>3.161168318374006</v>
       </c>
       <c r="G38">
-        <v>-5.957899908529575</v>
+        <v>-6.004453880014976</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.239392255370431</v>
       </c>
       <c r="E39">
-        <v>-29.69325142974221</v>
+        <v>-31.13745651060941</v>
       </c>
       <c r="F39">
-        <v>3.50760647683801</v>
+        <v>4.736726431968277</v>
       </c>
       <c r="G39">
-        <v>-5.72109414858445</v>
+        <v>-7.473565052489837</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.169463175464234</v>
       </c>
       <c r="E40">
-        <v>-26.97973546265804</v>
+        <v>-29.73218724926016</v>
       </c>
       <c r="F40">
-        <v>3.313579636815087</v>
+        <v>4.462568299602947</v>
       </c>
       <c r="G40">
-        <v>-5.849639284397256</v>
+        <v>-7.539543855607151</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.048146015683194</v>
       </c>
       <c r="E41">
-        <v>-28.8844161587582</v>
+        <v>-28.13402537331719</v>
       </c>
       <c r="F41">
-        <v>4.210736325477869</v>
+        <v>4.76478157916629</v>
       </c>
       <c r="G41">
-        <v>-6.869177166126359</v>
+        <v>-6.73674378276561</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.885339164672839</v>
       </c>
       <c r="E42">
-        <v>-27.1033356322234</v>
+        <v>-26.90125247963111</v>
       </c>
       <c r="F42">
-        <v>3.602192780359268</v>
+        <v>4.373397862161191</v>
       </c>
       <c r="G42">
-        <v>-7.155965774086505</v>
+        <v>-6.799661206167962</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.689833487678462</v>
       </c>
       <c r="E43">
-        <v>-25.27162676628284</v>
+        <v>-27.49445993226589</v>
       </c>
       <c r="F43">
-        <v>3.748093131014345</v>
+        <v>4.195676606094974</v>
       </c>
       <c r="G43">
-        <v>-8.635872165491939</v>
+        <v>-7.693439709188228</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.470883000088385</v>
       </c>
       <c r="E44">
-        <v>-25.87893135850349</v>
+        <v>-28.04384534192844</v>
       </c>
       <c r="F44">
-        <v>4.206054392917246</v>
+        <v>3.787609569597493</v>
       </c>
       <c r="G44">
-        <v>-7.198913683078077</v>
+        <v>-7.677568440505193</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.238358920532811</v>
       </c>
       <c r="E45">
-        <v>-25.13367133411317</v>
+        <v>-27.55807140665163</v>
       </c>
       <c r="F45">
-        <v>4.117473753066284</v>
+        <v>4.005592794909377</v>
       </c>
       <c r="G45">
-        <v>-8.632672974471481</v>
+        <v>-9.216825567477864</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.999815342419479</v>
       </c>
       <c r="E46">
-        <v>-25.7197690825559</v>
+        <v>-21.77855664114825</v>
       </c>
       <c r="F46">
-        <v>4.707180223445224</v>
+        <v>5.316638286176516</v>
       </c>
       <c r="G46">
-        <v>-8.467187846342446</v>
+        <v>-9.155161570711218</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.762234165003117</v>
       </c>
       <c r="E47">
-        <v>-24.76311989148752</v>
+        <v>-26.26533698862999</v>
       </c>
       <c r="F47">
-        <v>4.316033419517326</v>
+        <v>4.681361668234769</v>
       </c>
       <c r="G47">
-        <v>-6.855907906139964</v>
+        <v>-8.6431892895695</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.533162524761513</v>
       </c>
       <c r="E48">
-        <v>-23.47977300008379</v>
+        <v>-24.93911903379563</v>
       </c>
       <c r="F48">
-        <v>4.684718212950913</v>
+        <v>5.384269514410678</v>
       </c>
       <c r="G48">
-        <v>-9.300447498920311</v>
+        <v>-8.062186669260184</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.315376765083769</v>
       </c>
       <c r="E49">
-        <v>-24.05653756359671</v>
+        <v>-24.03740928938831</v>
       </c>
       <c r="F49">
-        <v>4.257172945344004</v>
+        <v>4.698061555075207</v>
       </c>
       <c r="G49">
-        <v>-8.048389132602718</v>
+        <v>-9.266240764163101</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.111867709877925</v>
       </c>
       <c r="E50">
-        <v>-23.36475881723697</v>
+        <v>-23.91954216791667</v>
       </c>
       <c r="F50">
-        <v>4.825152995482319</v>
+        <v>5.393992890984739</v>
       </c>
       <c r="G50">
-        <v>-8.964991812790482</v>
+        <v>-10.80086152507227</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.923751649596128</v>
       </c>
       <c r="E51">
-        <v>-21.44406090857168</v>
+        <v>-22.73735685737028</v>
       </c>
       <c r="F51">
-        <v>4.68711716494942</v>
+        <v>4.475679698854457</v>
       </c>
       <c r="G51">
-        <v>-9.548379881173515</v>
+        <v>-9.125870105850057</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.74945830427864</v>
       </c>
       <c r="E52">
-        <v>-21.57455341557671</v>
+        <v>-21.11857231079637</v>
       </c>
       <c r="F52">
-        <v>4.957471434201095</v>
+        <v>5.197550531615253</v>
       </c>
       <c r="G52">
-        <v>-9.417564140041572</v>
+        <v>-9.752770453332886</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.589885135327083</v>
       </c>
       <c r="E53">
-        <v>-20.21232956390737</v>
+        <v>-21.80830871537865</v>
       </c>
       <c r="F53">
-        <v>4.976436077520787</v>
+        <v>5.145645030155836</v>
       </c>
       <c r="G53">
-        <v>-8.87831506407619</v>
+        <v>-9.914987484788712</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.443877620111838</v>
       </c>
       <c r="E54">
-        <v>-19.52223540987848</v>
+        <v>-19.70289888041449</v>
       </c>
       <c r="F54">
-        <v>4.991913294074693</v>
+        <v>5.09209770450407</v>
       </c>
       <c r="G54">
-        <v>-9.59343761562781</v>
+        <v>-9.768254537871904</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.309147963319096</v>
       </c>
       <c r="E55">
-        <v>-19.30033112655462</v>
+        <v>-19.78822438766701</v>
       </c>
       <c r="F55">
-        <v>4.707940664720994</v>
+        <v>5.093689826652251</v>
       </c>
       <c r="G55">
-        <v>-8.703911575748585</v>
+        <v>-10.56858713210074</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.184766910869548</v>
       </c>
       <c r="E56">
-        <v>-19.50894433866597</v>
+        <v>-19.24191381185567</v>
       </c>
       <c r="F56">
-        <v>4.742306314793534</v>
+        <v>4.230935236227732</v>
       </c>
       <c r="G56">
-        <v>-9.976005080908147</v>
+        <v>-10.12351567733454</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.069984231875095</v>
       </c>
       <c r="E57">
-        <v>-18.38427064801699</v>
+        <v>-22.45962554647985</v>
       </c>
       <c r="F57">
-        <v>4.829916108048415</v>
+        <v>4.23982030499016</v>
       </c>
       <c r="G57">
-        <v>-10.56421654498356</v>
+        <v>-9.893364234711973</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.964165710666574</v>
       </c>
       <c r="E58">
-        <v>-18.3335607960791</v>
+        <v>-16.96096221045818</v>
       </c>
       <c r="F58">
-        <v>4.297413377037199</v>
+        <v>4.600231364804586</v>
       </c>
       <c r="G58">
-        <v>-9.183527731092619</v>
+        <v>-10.66796220825009</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.870169967844873</v>
       </c>
       <c r="E59">
-        <v>-19.43621251762877</v>
+        <v>-20.2715665324017</v>
       </c>
       <c r="F59">
-        <v>4.32084292065798</v>
+        <v>4.492028357916109</v>
       </c>
       <c r="G59">
-        <v>-10.6043032287753</v>
+        <v>-10.2602769919322</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.788548004540165</v>
       </c>
       <c r="E60">
-        <v>-18.4323358711344</v>
+        <v>-17.86829179110902</v>
       </c>
       <c r="F60">
-        <v>4.133486094962398</v>
+        <v>5.041681607634887</v>
       </c>
       <c r="G60">
-        <v>-10.93617582096222</v>
+        <v>-10.01821143382728</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.720456615291331</v>
       </c>
       <c r="E61">
-        <v>-17.03658772638628</v>
+        <v>-17.69331155545264</v>
       </c>
       <c r="F61">
-        <v>4.234462424628853</v>
+        <v>5.085821993060462</v>
       </c>
       <c r="G61">
-        <v>-9.803757355145096</v>
+        <v>-9.62397922590312</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.667551907809682</v>
       </c>
       <c r="E62">
-        <v>-16.36860158246284</v>
+        <v>-17.68584410181399</v>
       </c>
       <c r="F62">
-        <v>4.573448589937272</v>
+        <v>4.558021075427534</v>
       </c>
       <c r="G62">
-        <v>-9.763457391951997</v>
+        <v>-9.352563140948973</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.630056304160082</v>
       </c>
       <c r="E63">
-        <v>-15.58634392542984</v>
+        <v>-15.28771823546803</v>
       </c>
       <c r="F63">
-        <v>4.774425432469682</v>
+        <v>3.999610325526359</v>
       </c>
       <c r="G63">
-        <v>-9.727196612498574</v>
+        <v>-10.23428643595984</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.60876005220797</v>
       </c>
       <c r="E64">
-        <v>-14.88431724239075</v>
+        <v>-16.75305996876603</v>
       </c>
       <c r="F64">
-        <v>4.244598328169507</v>
+        <v>4.970904240004892</v>
       </c>
       <c r="G64">
-        <v>-9.13966764250752</v>
+        <v>-9.801385031957619</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.603920962279738</v>
       </c>
       <c r="E65">
-        <v>-14.57709198028837</v>
+        <v>-17.25746857458441</v>
       </c>
       <c r="F65">
-        <v>4.30076660828373</v>
+        <v>4.499882937629454</v>
       </c>
       <c r="G65">
-        <v>-9.727436141672413</v>
+        <v>-10.00030908899895</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.613227022737594</v>
       </c>
       <c r="E66">
-        <v>-14.26673754264669</v>
+        <v>-17.02387177137274</v>
       </c>
       <c r="F66">
-        <v>4.013626301981727</v>
+        <v>4.217437817766517</v>
       </c>
       <c r="G66">
-        <v>-9.356667949119839</v>
+        <v>-9.839555482358639</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.635861276313916</v>
       </c>
       <c r="E67">
-        <v>-15.4646411864737</v>
+        <v>-16.4862422802341</v>
       </c>
       <c r="F67">
-        <v>4.172464094733726</v>
+        <v>3.947424835884796</v>
       </c>
       <c r="G67">
-        <v>-10.12559269058167</v>
+        <v>-10.93500442486549</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.670102543616076</v>
       </c>
       <c r="E68">
-        <v>-14.64771806091199</v>
+        <v>-14.65605951003412</v>
       </c>
       <c r="F68">
-        <v>4.033782137626645</v>
+        <v>3.659966436500117</v>
       </c>
       <c r="G68">
-        <v>-9.463996706329274</v>
+        <v>-10.19060025211739</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.713519912005664</v>
       </c>
       <c r="E69">
-        <v>-14.94378063458547</v>
+        <v>-15.10294743900706</v>
       </c>
       <c r="F69">
-        <v>3.701987858109331</v>
+        <v>4.027370573928976</v>
       </c>
       <c r="G69">
-        <v>-9.278788155406417</v>
+        <v>-10.24065528700672</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.765301918381027</v>
       </c>
       <c r="E70">
-        <v>-15.42174295219904</v>
+        <v>-15.69964634510176</v>
       </c>
       <c r="F70">
-        <v>3.619876767674232</v>
+        <v>4.203832711542938</v>
       </c>
       <c r="G70">
-        <v>-9.007345820679793</v>
+        <v>-8.401067950698074</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.823203408919679</v>
       </c>
       <c r="E71">
-        <v>-15.54979008323993</v>
+        <v>-14.77355076816313</v>
       </c>
       <c r="F71">
-        <v>2.970599083890368</v>
+        <v>3.723923026935462</v>
       </c>
       <c r="G71">
-        <v>-7.104739343100454</v>
+        <v>-8.222910744906464</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.884826211275162</v>
       </c>
       <c r="E72">
-        <v>-14.41730024645371</v>
+        <v>-15.26832278129318</v>
       </c>
       <c r="F72">
-        <v>3.403813698002037</v>
+        <v>3.50441394886762</v>
       </c>
       <c r="G72">
-        <v>-8.614547506577107</v>
+        <v>-11.21644464168375</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.949009517733866</v>
       </c>
       <c r="E73">
-        <v>-16.33631356278815</v>
+        <v>-15.23365731276446</v>
       </c>
       <c r="F73">
-        <v>3.377151864775532</v>
+        <v>4.019709832187886</v>
       </c>
       <c r="G73">
-        <v>-7.49322613207403</v>
+        <v>-9.96859608262692</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.013976090869075</v>
       </c>
       <c r="E74">
-        <v>-14.80990988597072</v>
+        <v>-15.59844400797834</v>
       </c>
       <c r="F74">
-        <v>3.503310563487092</v>
+        <v>3.643278146803318</v>
       </c>
       <c r="G74">
-        <v>-6.909496816648815</v>
+        <v>-9.496602204965477</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.078061987939139</v>
       </c>
       <c r="E75">
-        <v>-13.22129403323591</v>
+        <v>-15.39255693721961</v>
       </c>
       <c r="F75">
-        <v>2.927686338955743</v>
+        <v>3.182596526349624</v>
       </c>
       <c r="G75">
-        <v>-6.940268112433287</v>
+        <v>-9.067198583145625</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.140422746051444</v>
       </c>
       <c r="E76">
-        <v>-15.02949559060265</v>
+        <v>-14.33535298081091</v>
       </c>
       <c r="F76">
-        <v>2.741091611270738</v>
+        <v>3.04627541634052</v>
       </c>
       <c r="G76">
-        <v>-7.93593510731743</v>
+        <v>-8.753822236889299</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.198590089300538</v>
       </c>
       <c r="E77">
-        <v>-14.97029032142637</v>
+        <v>-16.37759966031608</v>
       </c>
       <c r="F77">
-        <v>2.359545585541285</v>
+        <v>3.169498380976558</v>
       </c>
       <c r="G77">
-        <v>-7.141935270698319</v>
+        <v>-7.610828393986088</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.252298468744826</v>
       </c>
       <c r="E78">
-        <v>-15.32988285695345</v>
+        <v>-15.29583326088978</v>
       </c>
       <c r="F78">
-        <v>2.922325145124824</v>
+        <v>2.945420028314875</v>
       </c>
       <c r="G78">
-        <v>-7.38095257397451</v>
+        <v>-8.27440623606039</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.301492885751291</v>
       </c>
       <c r="E79">
-        <v>-15.51483026390071</v>
+        <v>-16.65011869762367</v>
       </c>
       <c r="F79">
-        <v>2.403270130530654</v>
+        <v>3.900429896389174</v>
       </c>
       <c r="G79">
-        <v>-5.503427753995566</v>
+        <v>-10.03002711266284</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.346041692715584</v>
       </c>
       <c r="E80">
-        <v>-16.51302820398947</v>
+        <v>-16.15418739514766</v>
       </c>
       <c r="F80">
-        <v>2.594551760980699</v>
+        <v>3.025403871259584</v>
       </c>
       <c r="G80">
-        <v>-6.644905672538312</v>
+        <v>-7.193053421372909</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.38661364276079</v>
       </c>
       <c r="E81">
-        <v>-16.29275417130837</v>
+        <v>-16.99477179739945</v>
       </c>
       <c r="F81">
-        <v>2.70001287176591</v>
+        <v>2.569354481322344</v>
       </c>
       <c r="G81">
-        <v>-5.19010062606263</v>
+        <v>-8.362021414140683</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.423572759845712</v>
       </c>
       <c r="E82">
-        <v>-16.54658419638631</v>
+        <v>-16.17512705895913</v>
       </c>
       <c r="F82">
-        <v>1.868288924250261</v>
+        <v>2.886436955765939</v>
       </c>
       <c r="G82">
-        <v>-6.219488734913186</v>
+        <v>-7.318012182021242</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.456065508914675</v>
       </c>
       <c r="E83">
-        <v>-16.21294434539718</v>
+        <v>-17.51303753368129</v>
       </c>
       <c r="F83">
-        <v>2.59550769696353</v>
+        <v>2.985216455080169</v>
       </c>
       <c r="G83">
-        <v>-5.870232230904331</v>
+        <v>-8.193612717602182</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.485676168026451</v>
       </c>
       <c r="E84">
-        <v>-18.49811195609582</v>
+        <v>-16.02945510708039</v>
       </c>
       <c r="F84">
-        <v>2.46208752959903</v>
+        <v>3.003692361632209</v>
       </c>
       <c r="G84">
-        <v>-5.054832267274522</v>
+        <v>-7.471317415721618</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.514001977959166</v>
       </c>
       <c r="E85">
-        <v>-18.83215484127162</v>
+        <v>-18.9755444422505</v>
       </c>
       <c r="F85">
-        <v>1.940259140940287</v>
+        <v>3.406934986375786</v>
       </c>
       <c r="G85">
-        <v>-4.739867809783424</v>
+        <v>-7.336646239257328</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.542621791587168</v>
       </c>
       <c r="E86">
-        <v>-19.60132520842244</v>
+        <v>-20.6070223014679</v>
       </c>
       <c r="F86">
-        <v>1.855025105396635</v>
+        <v>2.22743755214282</v>
       </c>
       <c r="G86">
-        <v>-4.774606102433265</v>
+        <v>-7.003641625632403</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.576072175181913</v>
       </c>
       <c r="E87">
-        <v>-21.64346773302544</v>
+        <v>-22.69006600330817</v>
       </c>
       <c r="F87">
-        <v>2.157409028644956</v>
+        <v>3.1740676555704</v>
       </c>
       <c r="G87">
-        <v>-5.457995960283494</v>
+        <v>-6.984085545138113</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.617183105054027</v>
       </c>
       <c r="E88">
-        <v>-22.02738723092173</v>
+        <v>-23.43171683391439</v>
       </c>
       <c r="F88">
-        <v>2.009793957466083</v>
+        <v>3.059698281735483</v>
       </c>
       <c r="G88">
-        <v>-4.540753441891639</v>
+        <v>-6.999513848910621</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.670233533154898</v>
       </c>
       <c r="E89">
-        <v>-23.39763101005865</v>
+        <v>-24.84620380410625</v>
       </c>
       <c r="F89">
-        <v>1.617344959980984</v>
+        <v>2.432745099457066</v>
       </c>
       <c r="G89">
-        <v>-4.962997438268783</v>
+        <v>-6.515484450569134</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.740782140366539</v>
       </c>
       <c r="E90">
-        <v>-24.81229911921082</v>
+        <v>-25.65093627763931</v>
       </c>
       <c r="F90">
-        <v>0.9088240962837054</v>
+        <v>3.035254816413675</v>
       </c>
       <c r="G90">
-        <v>-4.898029251391778</v>
+        <v>-6.036885473908528</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.833142383785184</v>
       </c>
       <c r="E91">
-        <v>-25.066858228604</v>
+        <v>-26.88770328540016</v>
       </c>
       <c r="F91">
-        <v>1.383379213999486</v>
+        <v>2.820000233326613</v>
       </c>
       <c r="G91">
-        <v>-4.492270112129285</v>
+        <v>-5.286788381754787</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.951602718167477</v>
       </c>
       <c r="E92">
-        <v>-28.58475344824863</v>
+        <v>-28.79159149854897</v>
       </c>
       <c r="F92">
-        <v>1.62441259066167</v>
+        <v>1.627066679820239</v>
       </c>
       <c r="G92">
-        <v>-5.106741192344937</v>
+        <v>-6.383119972861135</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.099929701342671</v>
       </c>
       <c r="E93">
-        <v>-29.41945536276446</v>
+        <v>-29.4622245355299</v>
       </c>
       <c r="F93">
-        <v>1.524743424756833</v>
+        <v>2.005527865341666</v>
       </c>
       <c r="G93">
-        <v>-4.563295434005025</v>
+        <v>-7.572743255345613</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.276538653237209</v>
       </c>
       <c r="E94">
-        <v>-31.09885579816804</v>
+        <v>-32.55140006392036</v>
       </c>
       <c r="F94">
-        <v>1.008441903409568</v>
+        <v>1.006341163676069</v>
       </c>
       <c r="G94">
-        <v>-3.750330136772324</v>
+        <v>-5.491008330393067</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.483142211978274</v>
       </c>
       <c r="E95">
-        <v>-33.61319362873584</v>
+        <v>-35.1115751083938</v>
       </c>
       <c r="F95">
-        <v>0.995903734400795</v>
+        <v>1.145786875528532</v>
       </c>
       <c r="G95">
-        <v>-4.126184222742038</v>
+        <v>-6.060762923196607</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.719876209444281</v>
       </c>
       <c r="E96">
-        <v>-35.77247871896925</v>
+        <v>-35.96125268645299</v>
       </c>
       <c r="F96">
-        <v>0.814100283773582</v>
+        <v>0.9748963370657996</v>
       </c>
       <c r="G96">
-        <v>-4.568299296883178</v>
+        <v>-5.761610672400473</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.980230352585064</v>
       </c>
       <c r="E97">
-        <v>-36.03153460305204</v>
+        <v>-38.58164737828043</v>
       </c>
       <c r="F97">
-        <v>0.9109182090779826</v>
+        <v>0.9031017342651665</v>
       </c>
       <c r="G97">
-        <v>-4.271312652316277</v>
+        <v>-6.762865587600349</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.26531269208922</v>
       </c>
       <c r="E98">
-        <v>-39.93099451410897</v>
+        <v>-39.6076592057243</v>
       </c>
       <c r="F98">
-        <v>0.772226311562067</v>
+        <v>0.9916823741161288</v>
       </c>
       <c r="G98">
-        <v>-3.747816721057789</v>
+        <v>-6.421503702663519</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.560531286247778</v>
       </c>
       <c r="E99">
-        <v>-42.32188387899067</v>
+        <v>-41.20269869883899</v>
       </c>
       <c r="F99">
-        <v>0.9596957952244287</v>
+        <v>1.145334586926603</v>
       </c>
       <c r="G99">
-        <v>-4.392478320841892</v>
+        <v>-6.840525539469287</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.868616228164296</v>
       </c>
       <c r="E100">
-        <v>-43.87922609022851</v>
+        <v>-44.20056434157579</v>
       </c>
       <c r="F100">
-        <v>0.5258880700523556</v>
+        <v>1.311349354856458</v>
       </c>
       <c r="G100">
-        <v>-5.012560289924195</v>
+        <v>-6.639944465540432</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.16414505936873</v>
       </c>
       <c r="E101">
-        <v>-45.31694866055373</v>
+        <v>-47.5268688829039</v>
       </c>
       <c r="F101">
-        <v>0.1315015212121082</v>
+        <v>0.724270465879198</v>
       </c>
       <c r="G101">
-        <v>-4.369342427626248</v>
+        <v>-7.766450170107432</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.469487347275718</v>
       </c>
       <c r="E102">
-        <v>-45.63479998691511</v>
+        <v>-50.73999780183232</v>
       </c>
       <c r="F102">
-        <v>0.606531293449693</v>
+        <v>1.226884044262604</v>
       </c>
       <c r="G102">
-        <v>-5.891599545699434</v>
+        <v>-7.430659799378538</v>
       </c>
     </row>
   </sheetData>
